--- a/FINAL_SUBMISSION/06_技术分析/06_技术分析记录.xlsx
+++ b/FINAL_SUBMISSION/06_技术分析/06_技术分析记录.xlsx
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,17 +522,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>33.86</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>33.54</v>
+        <v>33.48</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>30.6</v>
+        <v>30.73</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>52.7</v>
+        <v>59.4</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -546,19 +546,19 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；RSI=52.7中性区</t>
+          <t>价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望</t>
+          <t>中期趋势向上，可关注/持有</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>58.24</t>
+          <t>55.70</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>54.37</v>
+        <v>54.68</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>52.56</v>
+        <v>52.62</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>84.90000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -597,7 +597,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.9超买区，短期回调风险</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>28.21</v>
+        <v>28.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>27.66</v>
+        <v>27.68</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>59.7</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=59.7中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -675,21 +675,21 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>351.00</t>
+          <t>335.49</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>379.27</v>
+        <v>374.24</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>382.3</v>
+        <v>380.52</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>344.76</t>
+          <t>326.00</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.6超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -711,46 +711,46 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1330.00</t>
+          <t>40.90</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1311.28</v>
+        <v>39.69</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1270.43</v>
+        <v>38.3</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>63.6</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1151.01</t>
+          <t>34.28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1363.35</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>价格站上60日均线；MACD红柱放大；RSI=63.6中性区</t>
+          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -762,97 +762,97 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>39.48</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>38.2</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>84</v>
+        <v>52.2</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>72.28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>89.50</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.0超买区，短期回调风险</t>
+          <t>价格站上60日均线；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有</t>
+          <t>趋势中性，观望</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>1309.30</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>85.58</v>
+        <v>1307.78</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>82.23999999999999</v>
+        <v>1272.4</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>75.7</v>
+        <v>50.5</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72.28</t>
+          <t>1151.01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89.50</t>
+          <t>1363.35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.7超买区，短期回调风险</t>
+          <t>价格站上60日均线；RSI=50.5中性区</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -883,13 +883,13 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>4.77</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>27</v>
+        <v>44.7</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>价格位于60日均线下方，中期趋势偏弱；RSI=27.0超卖区</t>
+          <t>价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
